--- a/Simulation/Results/p.mid_Censor.Ints_mean.surv.70.xlsx
+++ b/Simulation/Results/p.mid_Censor.Ints_mean.surv.70.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">mid</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9 mins</t>
+    <t xml:space="preserve">5.5 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8 mins</t>
   </si>
 </sst>
 </file>
@@ -419,13 +419,13 @@
         <v>50</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0132</v>
+        <v>0.0106</v>
       </c>
       <c r="C2" t="n">
         <v>0.0001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009</v>
+        <v>0.0006</v>
       </c>
       <c r="E2" t="n">
         <v>0.0142857142857143</v>
@@ -448,7 +448,7 @@
         <v>100</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0117</v>
+        <v>0.0109</v>
       </c>
       <c r="C3" t="n">
         <v>0.0001</v>
@@ -477,7 +477,7 @@
         <v>200</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0122</v>
+        <v>0.0118</v>
       </c>
       <c r="C4" t="n">
         <v>0.0001</v>
@@ -506,7 +506,7 @@
         <v>500</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0089</v>
+        <v>0.0101</v>
       </c>
       <c r="C5" t="n">
         <v>0.0001</v>
